--- a/src/main/resources/sample-data/ftes.xlsx
+++ b/src/main/resources/sample-data/ftes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pete/IdeaProjects/wfm-service/src/main/resources/sample-data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEAC5215-3927-774C-A23C-BEB8333BD889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA5099C1-43CB-F446-B39F-CB63750E4B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="920" windowWidth="29100" windowHeight="18060" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3500" yWindow="7440" windowWidth="29100" windowHeight="18060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026-01-19" sheetId="1" r:id="rId1"/>
@@ -533,46 +533,46 @@
         <v>15</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="K2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="N2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O2">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
@@ -580,46 +580,46 @@
         <v>16</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O3">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
@@ -627,46 +627,46 @@
         <v>17</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="J4">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K4">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="L4">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="N4">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O4">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
@@ -674,46 +674,46 @@
         <v>18</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="O5">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
